--- a/pacjenci/JÓZEF OKŁA.xlsx
+++ b/pacjenci/JÓZEF OKŁA.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>19.05.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>NHL DLBCL. Zaawansowanie procesu przed podjęciem terapii.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  59 min od podania 18F-FDG. Glikemia: 72 mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Asymetrycznie wzmożony metabolizm FDG w topografii lewego migdałka podniebiennego SUV max 4,6- do oceny w badaniu laryngologicznym Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Lewa zatoka klinowa niemal całkowicie zajęta przez masy śluzówkowe w wysokim cieniowaniem - być może na podłożu zmian grzybiczych.  Klatka piersiowa i śródpiersie: Wzmożony metabolizm FDG w węzłach chłonnych: - przytchawiczych dolnych prawych wielkości do 18x8 mm SUV max do 1,9 - we wnęce płuca lewego SUV max do 3,2 - we wnęce płuca prawego SUV max do  2,7 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zmiany rozedmowe, zmiany włókniste na obwodzie płatów dolnych obu płuc.  Brzuch i miednica: Aktywne metabolicznie pojedyncze i spakietowane węzły chłonne: - przy naczyniach biodrowych zewnętrznych prawych o największych wymiarach 42x58x72 mm SUV max 13,8 [Im fuz. 254] oraz wielkości 13 mm SUV max 5,4 [Im fuz. 241] - przy naczyniach biodrowych zewnętrznych lewych wielkości 12 mm SUV max 4,0 - pachwinowe i udowe prawe wielkości do 20x28 mm SUV max do 11,6 [Im fuz. 277] - pachwinowe lewe wielkości do 10x7 mm SUV max do 4,9.  Rozlanie wzmożony metabolizm FDG w jelitach  SUV max do 5,0- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona dodatkowa 17 mm.  Układ kostny: Wzmożony metabolizm FDG w prawym stawie ramiennym SUV max do 3,1- zmiany odczynowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym.  Inne: Miażdżyca aorty i tt potomnych.  Wartości referencyjne: MBPS SUVmax 1,2 Prawy płat wątroby SUVmax do 2,5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych po obu stronach przepony. Asymetrycznie wzmożony metabolizm FDG w topografii lewego migdałka podniebiennego - do oceny w badaniu laryngologicznym Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>13.8</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>13.12.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>NHL DLBCL. Ocena po 4 cyklach RCHOP i powikłaniach infekcyjnych.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 95mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Asymetrycznie wzmożony metabolizm FDG w topografii lewego fałdu głosowego, SUV max 4,4 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie pogrubienie błony śluzowej w hypoplastycznej lewej zatoce klinowej. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie przylegające do siebie spikularne nacieki/zmiany guzkowe obwodowo w przedniej części segmentu 3 płuca lewego, wielkości 15x12mm i 12x10mm, SUV max 4,9.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Rozsiane zmiany rozedmowe w miąższu obu płuc, z nielicznymi wydatniejszymi pęcherzami rozedmowymi, wielkości do 28x13mm. Niewielkie zmiany włókniste w szczytach [ze zwapnieniami po stronie lewej] oraz na obwodzie płatów górnych i dolnych obu płuc. Drobne zwapnienie oraz niewielkie obwodowe zmiany miąższowo-włókniste w segm. 3 płuca prawego. Niewielkie nieregularne zmiany miąższowo-włókniste w segm. 10 płuca prawego. Osełkowato zwiększona ilość płynu  w worku osierdziowym od strony PK, o szerokości do 14mm  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w jelitach (głownie we wstępnicy) SUV max do 6,1 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne: - przy naczyniach biodrowych zewnętrznych prawych wielkości do 29x16mm, - przy naczyniach biodrowych zewnętrznych lewych średnicy do 10mm, - pachwinowe obustronnie średnicy do 12mm. Śledziona dodatkowa wielkości 19x17 mm. Guzkowe pogrubienie trzonu nadnercza prawego wielkości  14x23mm. Cechy wydatnej lipofibromatozy we wnękach obu nerek. Prostata miernie powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych z wydatnymi mostami kostnymi na przednich krawędziach.  Inne: Miażdżyca aorty i tt potomnych.  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Aktywne metabolicznie zmiany w segmencie 3 płuca lewego - do oceny klinicznej i kontroli po leczeniu p/zapalnym. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>6.1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>28.03.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>NHL DLBCL. Ocena po zakończonej immunochemioterapii - po 6 cyklach RCHOP.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  61min od podania 18F-FDG. Glikemia: 104mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Asymetrycznie wzmożony metabolizm FDG w topografii lewego fałdu głosowego, SUV max 5,4 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie pogrubienie błony śluzowej w hypoplastycznej lewej zatoce klinowej. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Rozsiane zmiany rozedmowe w miąższu obu płuc, z nielicznymi wydatniejszymi pęcherzami rozedmowymi, wielkości do 28x13mm. Niewielkie zmiany włókniste w szczytach [ze zwapnieniami po stronie lewej] oraz na obwodzie płatów górnych i dolnych obu płuc. Drobne zwapnienie oraz niewielkie obwodowe zmiany miąższowo-włókniste w segm. 3 płuca prawego. Niewielkie nieregularne zmiany miąższowo-włókniste w segm. 10 płuca prawego. Osełkowato zwiększona ilość płynu  w worku osierdziowym od strony PK, o szerokości do 14mm  Brzuch i miednica: Niejednorodny metabolizm FDG w wątrobie. Rozlanie wzmożony metabolizm FDG w jelitach (głownie we wstępnicy) SUV max do 6,5 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne: - przy naczyniach biodrowych zewnętrznych prawych wielkości do 21x14mm, - przy naczyniach biodrowych zewnętrznych lewych średnicy do 7mm, - pachwinowe obustronnie średnicy do 12mm. Śledziona dodatkowa wielkości 19x17 mm. Guzkowe pogrubienie trzonu nadnercza prawego wielkości  14x23mm. Cechy wydatnej lipofibromatozy we wnękach obu nerek. Prostata miernie powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych z wydatnymi mostami kostnymi na przednich krawędziach.  Inne: Miażdżyca aorty i tt potomnych.  Wartości referencyjne: MBPS SUVmax 2,2; Prawy płat wątroby SUVmax do 2,9.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>6.5</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/JÓZEF OKŁA.xlsx
+++ b/pacjenci/JÓZEF OKŁA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  59 min od podania 18F-FDG. Glikemia: 72 mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Asymetrycznie wzmożony metabolizm FDG w topografii lewego migdałka podniebiennego SUV max 4,6- do oceny w badaniu laryngologicznym Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Lewa zatoka klinowa niemal całkowicie zajęta przez masy śluzówkowe w wysokim cieniowaniem - być może na podłożu zmian grzybiczych.  Klatka piersiowa i śródpiersie: Wzmożony metabolizm FDG w węzłach chłonnych: - przytchawiczych dolnych prawych wielkości do 18x8 mm SUV max do 1,9 - we wnęce płuca lewego SUV max do 3,2 - we wnęce płuca prawego SUV max do  2,7 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zmiany rozedmowe, zmiany włókniste na obwodzie płatów dolnych obu płuc.  Brzuch i miednica: Aktywne metabolicznie pojedyncze i spakietowane węzły chłonne: - przy naczyniach biodrowych zewnętrznych prawych o największych wymiarach 42x58x72 mm SUV max 13,8 [Im fuz. 254] oraz wielkości 13 mm SUV max 5,4 [Im fuz. 241] - przy naczyniach biodrowych zewnętrznych lewych wielkości 12 mm SUV max 4,0 - pachwinowe i udowe prawe wielkości do 20x28 mm SUV max do 11,6 [Im fuz. 277] - pachwinowe lewe wielkości do 10x7 mm SUV max do 4,9.  Rozlanie wzmożony metabolizm FDG w jelitach  SUV max do 5,0- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona dodatkowa 17 mm.  Układ kostny: Wzmożony metabolizm FDG w prawym stawie ramiennym SUV max do 3,1- zmiany odczynowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym.  Inne: Miażdżyca aorty i tt potomnych.  Wartości referencyjne: MBPS SUVmax 1,2 Prawy płat wątroby SUVmax do 2,5</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Asymetrycznie wzmożony metabolizm FDG w topografii lewego migdałka podniebiennego SUV max 4,6- do oceny w badaniu laryngologicznym Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Lewa zatoka klinowa niemal całkowicie zajęta przez masy śluzówkowe w wysokim cieniowaniem - być może na podłożu zmian grzybiczych.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w węzłach chłonnych: - przytchawiczych dolnych prawych wielkości do 18x8 mm SUV max do 1,9 - we wnęce płuca lewego SUV max do 3,2 - we wnęce płuca prawego SUV max do  2,7 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zmiany rozedmowe, zmiany włókniste na obwodzie płatów dolnych obu płuc.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie pojedyncze i spakietowane węzły chłonne: - przy naczyniach biodrowych zewnętrznych prawych o największych wymiarach 42x58x72 mm SUV max 13,8 [Im fuz. 254] oraz wielkości 13 mm SUV max 5,4 [Im fuz. 241] - przy naczyniach biodrowych zewnętrznych lewych wielkości 12 mm SUV max 4,0 - pachwinowe i udowe prawe wielkości do 20x28 mm SUV max do 11,6 [Im fuz. 277] - pachwinowe lewe wielkości do 10x7 mm SUV max do 4,9.  Rozlanie wzmożony metabolizm FDG w jelitach  SUV max do 5,0- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona dodatkowa 17 mm.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w prawym stawie ramiennym SUV max do 3,1- zmiany odczynowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym.  Inne: Miażdżyca aorty i tt potomnych.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych po obu stronach przepony. Asymetrycznie wzmożony metabolizm FDG w topografii lewego migdałka podniebiennego - do oceny w badaniu laryngologicznym Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>13.8</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 95mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Asymetrycznie wzmożony metabolizm FDG w topografii lewego fałdu głosowego, SUV max 4,4 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie pogrubienie błony śluzowej w hypoplastycznej lewej zatoce klinowej. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie przylegające do siebie spikularne nacieki/zmiany guzkowe obwodowo w przedniej części segmentu 3 płuca lewego, wielkości 15x12mm i 12x10mm, SUV max 4,9.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Rozsiane zmiany rozedmowe w miąższu obu płuc, z nielicznymi wydatniejszymi pęcherzami rozedmowymi, wielkości do 28x13mm. Niewielkie zmiany włókniste w szczytach [ze zwapnieniami po stronie lewej] oraz na obwodzie płatów górnych i dolnych obu płuc. Drobne zwapnienie oraz niewielkie obwodowe zmiany miąższowo-włókniste w segm. 3 płuca prawego. Niewielkie nieregularne zmiany miąższowo-włókniste w segm. 10 płuca prawego. Osełkowato zwiększona ilość płynu  w worku osierdziowym od strony PK, o szerokości do 14mm  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w jelitach (głownie we wstępnicy) SUV max do 6,1 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne: - przy naczyniach biodrowych zewnętrznych prawych wielkości do 29x16mm, - przy naczyniach biodrowych zewnętrznych lewych średnicy do 10mm, - pachwinowe obustronnie średnicy do 12mm. Śledziona dodatkowa wielkości 19x17 mm. Guzkowe pogrubienie trzonu nadnercza prawego wielkości  14x23mm. Cechy wydatnej lipofibromatozy we wnękach obu nerek. Prostata miernie powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych z wydatnymi mostami kostnymi na przednich krawędziach.  Inne: Miażdżyca aorty i tt potomnych.  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 2,7.</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Asymetrycznie wzmożony metabolizm FDG w topografii lewego fałdu głosowego, SUV max 4,4 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie pogrubienie błony śluzowej w hypoplastycznej lewej zatoce klinowej. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie przylegające do siebie spikularne nacieki/zmiany guzkowe obwodowo w przedniej części segmentu 3 płuca lewego, wielkości 15x12mm i 12x10mm, SUV max 4,9.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Rozsiane zmiany rozedmowe w miąższu obu płuc, z nielicznymi wydatniejszymi pęcherzami rozedmowymi, wielkości do 28x13mm. Niewielkie zmiany włókniste w szczytach [ze zwapnieniami po stronie lewej] oraz na obwodzie płatów górnych i dolnych obu płuc. Drobne zwapnienie oraz niewielkie obwodowe zmiany miąższowo-włókniste w segm. 3 płuca prawego. Niewielkie nieregularne zmiany miąższowo-włókniste w segm. 10 płuca prawego. Osełkowato zwiększona ilość płynu  w worku osierdziowym od strony PK, o szerokości do 14mm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w jelitach (głownie we wstępnicy) SUV max do 6,1 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne: - przy naczyniach biodrowych zewnętrznych prawych wielkości do 29x16mm, - przy naczyniach biodrowych zewnętrznych lewych średnicy do 10mm, - pachwinowe obustronnie średnicy do 12mm. Śledziona dodatkowa wielkości 19x17 mm. Guzkowe pogrubienie trzonu nadnercza prawego wielkości  14x23mm. Cechy wydatnej lipofibromatozy we wnękach obu nerek. Prostata miernie powiększona.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych z wydatnymi mostami kostnymi na przednich krawędziach.  Inne: Miażdżyca aorty i tt potomnych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Aktywne metabolicznie zmiany w segmencie 3 płuca lewego - do oceny klinicznej i kontroli po leczeniu p/zapalnym. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>6.1</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  61min od podania 18F-FDG. Glikemia: 104mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Asymetrycznie wzmożony metabolizm FDG w topografii lewego fałdu głosowego, SUV max 5,4 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie pogrubienie błony śluzowej w hypoplastycznej lewej zatoce klinowej. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Rozsiane zmiany rozedmowe w miąższu obu płuc, z nielicznymi wydatniejszymi pęcherzami rozedmowymi, wielkości do 28x13mm. Niewielkie zmiany włókniste w szczytach [ze zwapnieniami po stronie lewej] oraz na obwodzie płatów górnych i dolnych obu płuc. Drobne zwapnienie oraz niewielkie obwodowe zmiany miąższowo-włókniste w segm. 3 płuca prawego. Niewielkie nieregularne zmiany miąższowo-włókniste w segm. 10 płuca prawego. Osełkowato zwiększona ilość płynu  w worku osierdziowym od strony PK, o szerokości do 14mm  Brzuch i miednica: Niejednorodny metabolizm FDG w wątrobie. Rozlanie wzmożony metabolizm FDG w jelitach (głownie we wstępnicy) SUV max do 6,5 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne: - przy naczyniach biodrowych zewnętrznych prawych wielkości do 21x14mm, - przy naczyniach biodrowych zewnętrznych lewych średnicy do 7mm, - pachwinowe obustronnie średnicy do 12mm. Śledziona dodatkowa wielkości 19x17 mm. Guzkowe pogrubienie trzonu nadnercza prawego wielkości  14x23mm. Cechy wydatnej lipofibromatozy we wnękach obu nerek. Prostata miernie powiększona.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych z wydatnymi mostami kostnymi na przednich krawędziach.  Inne: Miażdżyca aorty i tt potomnych.  Wartości referencyjne: MBPS SUVmax 2,2; Prawy płat wątroby SUVmax do 2,9.</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Asymetrycznie wzmożony metabolizm FDG w topografii lewego fałdu głosowego, SUV max 5,4 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie pogrubienie błony śluzowej w hypoplastycznej lewej zatoce klinowej. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Rozsiane zmiany rozedmowe w miąższu obu płuc, z nielicznymi wydatniejszymi pęcherzami rozedmowymi, wielkości do 28x13mm. Niewielkie zmiany włókniste w szczytach [ze zwapnieniami po stronie lewej] oraz na obwodzie płatów górnych i dolnych obu płuc. Drobne zwapnienie oraz niewielkie obwodowe zmiany miąższowo-włókniste w segm. 3 płuca prawego. Niewielkie nieregularne zmiany miąższowo-włókniste w segm. 10 płuca prawego. Osełkowato zwiększona ilość płynu  w worku osierdziowym od strony PK, o szerokości do 14mm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w wątrobie. Rozlanie wzmożony metabolizm FDG w jelitach (głownie we wstępnicy) SUV max do 6,5 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne: - przy naczyniach biodrowych zewnętrznych prawych wielkości do 21x14mm, - przy naczyniach biodrowych zewnętrznych lewych średnicy do 7mm, - pachwinowe obustronnie średnicy do 12mm. Śledziona dodatkowa wielkości 19x17 mm. Guzkowe pogrubienie trzonu nadnercza prawego wielkości  14x23mm. Cechy wydatnej lipofibromatozy we wnękach obu nerek. Prostata miernie powiększona.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, nasilone w odcinku piersiowym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych z wydatnymi mostami kostnymi na przednich krawędziach.  Inne: Miażdżyca aorty i tt potomnych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>6.5</v>
       </c>
     </row>
